--- a/assets/ESR Formations-Bavaria.xlsx
+++ b/assets/ESR Formations-Bavaria.xlsx
@@ -5,20 +5,20 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR_NewRecruit/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9efa18f7c2e81ea4/Documents/NewRecruit/ESR/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="106" documentId="8_{CBA1ACD2-9F58-43EB-88FE-AE8D1B64C06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{094417F5-20F5-47FD-B1A8-1C8CEC56A43A}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="8_{CBA1ACD2-9F58-43EB-88FE-AE8D1B64C06A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A0D60A2A-6891-4CF5-9D17-DE67E6C8FCC1}"/>
   <bookViews>
-    <workbookView xWindow="600" yWindow="375" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
+    <workbookView xWindow="2190" yWindow="1605" windowWidth="26610" windowHeight="14595" activeTab="1" xr2:uid="{20271C60-C4FB-4B77-A1B3-909BAACA5FD5}"/>
   </bookViews>
   <sheets>
     <sheet name="BaselineFormations" sheetId="1" r:id="rId1"/>
     <sheet name="ExpandedFormations" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$2)</definedName>
-    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$2)</definedName>
+    <definedName name="FromArray_1">_xlfn.ANCHORARRAY(ExpandedFormations!$A$3)</definedName>
+    <definedName name="FromArray_3">_xlfn.ANCHORARRAY(ExpandedFormations!$D$3)</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -77,7 +77,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="43">
   <si>
     <t>Formation</t>
   </si>
@@ -200,6 +200,12 @@
   </si>
   <si>
     <t>BV Korps Reservieren</t>
+  </si>
+  <si>
+    <t>BV Mixed</t>
+  </si>
+  <si>
+    <t>Mixed</t>
   </si>
 </sst>
 </file>
@@ -383,10 +389,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1060,7 +1062,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A52F401-E5BC-41DA-8596-65382229DEB1}">
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="40.5703125" customWidth="1"/>
@@ -1106,50 +1108,53 @@
         <v>BV Pioniere</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" t="str" cm="1">
-        <f t="array" ref="A2:C5">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
+    <row r="2" spans="1:11" s="7" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="str" cm="1">
+        <f t="array" ref="A3:C6">_xlfn.LET(_xlpm.data,_xlfn._xlws.FILTER(BaselineFormations!A:C,(BaselineFormations!A:A&lt;&gt;"Formation")*(NOT(ISBLANK(BaselineFormations!A:A)))),IF(_xlpm.data=0,"",_xlpm.data))</f>
         <v>BV Infanterie-Division</v>
       </c>
-      <c r="B2" t="str">
+      <c r="B3" t="str">
         <v>Infantry</v>
       </c>
-      <c r="C2" t="str">
+      <c r="C3" t="str">
         <v/>
       </c>
-      <c r="D2" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" t="str">
-        <v>BV Kavallerie-Division</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Cavalry</v>
-      </c>
-      <c r="C3" t="str">
-        <v>Rapid Deployment</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
-      </c>
-      <c r="G3" t="s">
+      <c r="D3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" t="s">
         <v>15</v>
       </c>
       <c r="H3" t="s">
@@ -1159,12 +1164,15 @@
         <v>15</v>
       </c>
       <c r="J3" t="s">
+        <v>15</v>
+      </c>
+      <c r="K3" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="str">
-        <v>BV Leichtes Kavallerie-Division</v>
+        <v>BV Kavallerie-Division</v>
       </c>
       <c r="B4" t="str">
         <v>Cavalry</v>
@@ -1172,7 +1180,16 @@
       <c r="C4" t="str">
         <v>Rapid Deployment</v>
       </c>
+      <c r="F4" t="s">
+        <v>15</v>
+      </c>
       <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>15</v>
+      </c>
+      <c r="I4" t="s">
         <v>15</v>
       </c>
       <c r="J4" t="s">
@@ -1181,24 +1198,41 @@
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="str">
+        <v>BV Leichtes Kavallerie-Division</v>
+      </c>
+      <c r="B5" t="str">
+        <v>Cavalry</v>
+      </c>
+      <c r="C5" t="str">
+        <v>Rapid Deployment</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="str">
         <v>BV Korps Reservieren</v>
       </c>
-      <c r="B5" t="str">
+      <c r="B6" t="str">
         <v>Artillery</v>
       </c>
-      <c r="C5" t="str">
+      <c r="C6" t="str">
         <v>Reinforcements</v>
       </c>
-      <c r="H5" t="s">
-        <v>15</v>
-      </c>
-      <c r="I5" t="s">
-        <v>15</v>
-      </c>
-      <c r="J5" t="s">
-        <v>15</v>
-      </c>
-      <c r="K5" t="s">
+      <c r="H6" t="s">
+        <v>15</v>
+      </c>
+      <c r="I6" t="s">
+        <v>15</v>
+      </c>
+      <c r="J6" t="s">
+        <v>15</v>
+      </c>
+      <c r="K6" t="s">
         <v>15</v>
       </c>
     </row>
